--- a/exampleAdvanced.xlsx
+++ b/exampleAdvanced.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronste\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajnyga/www/Sheet2OJS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5F6F45-6411-43CA-8BDE-7E612E16588C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B78BC94-B88F-2F44-B7AC-CC2EA23B12B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="27860" windowHeight="18180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Esimerkki" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="113">
   <si>
     <t>title</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>ARTICLE COVER ALT TEXT DE</t>
+  </si>
+  <si>
+    <t>articleDatePublished</t>
   </si>
 </sst>
 </file>
@@ -445,8 +448,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -724,37 +727,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AW5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25.44140625" style="6" customWidth="1"/>
+    <col min="1" max="2" width="25.5" style="6" customWidth="1"/>
     <col min="3" max="3" width="32" style="6" customWidth="1"/>
-    <col min="4" max="4" width="37.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="33.77734375" style="6" customWidth="1"/>
-    <col min="6" max="8" width="31.109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="35.88671875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="19" style="6" customWidth="1"/>
-    <col min="11" max="11" width="23" style="7" customWidth="1"/>
-    <col min="12" max="12" width="41.109375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="20" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="16.77734375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.44140625" style="3" customWidth="1"/>
-    <col min="18" max="20" width="8.77734375" style="4"/>
-    <col min="21" max="21" width="24.77734375" style="3" customWidth="1"/>
-    <col min="22" max="27" width="21.44140625" style="3" customWidth="1"/>
-    <col min="28" max="28" width="14.77734375" style="3" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" style="3" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.44140625" style="3" customWidth="1"/>
-    <col min="32" max="37" width="20.6640625" style="3" customWidth="1"/>
-    <col min="38" max="40" width="25.109375" style="3" customWidth="1"/>
-    <col min="41" max="41" width="34.33203125" style="3" customWidth="1"/>
-    <col min="42" max="16384" width="8.77734375" style="3"/>
+    <col min="4" max="4" width="37.1640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="31.1640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="35.83203125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="23" style="7" customWidth="1"/>
+    <col min="11" max="11" width="19" style="6" customWidth="1"/>
+    <col min="12" max="12" width="23" style="7" customWidth="1"/>
+    <col min="13" max="13" width="41.1640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="20" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="16.83203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.5" style="3" customWidth="1"/>
+    <col min="19" max="21" width="8.83203125" style="4"/>
+    <col min="22" max="22" width="24.83203125" style="3" customWidth="1"/>
+    <col min="23" max="28" width="21.5" style="3" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" style="3" customWidth="1"/>
+    <col min="30" max="30" width="13.5" style="3" customWidth="1"/>
+    <col min="31" max="31" width="16.6640625" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.5" style="3" customWidth="1"/>
+    <col min="33" max="38" width="20.6640625" style="3" customWidth="1"/>
+    <col min="39" max="41" width="25.1640625" style="3" customWidth="1"/>
+    <col min="42" max="42" width="34.33203125" style="3" customWidth="1"/>
+    <col min="43" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" s="1" customFormat="1" ht="20" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -782,125 +786,128 @@
       <c r="I1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:48" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:49" ht="40" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>57</v>
       </c>
@@ -928,104 +935,105 @@
       <c r="I2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="10">
+      <c r="L2" s="10">
         <v>42808</v>
       </c>
-      <c r="L2" s="6">
+      <c r="M2" s="6">
         <v>1</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>1</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="3">
         <v>2017</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AG2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AL2" s="3">
+      <c r="AM2" s="3">
         <v>2017</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AN2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AN2" s="5" t="s">
+      <c r="AO2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AP2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:49" ht="20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
@@ -1041,83 +1049,86 @@
       <c r="I3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="10">
+        <v>42992</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="10">
+      <c r="L3" s="10">
         <v>42808</v>
       </c>
-      <c r="L3" s="6">
+      <c r="M3" s="6">
         <v>1</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>1</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="3">
         <v>2017</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="3">
+      <c r="AM3" s="3">
         <v>2017</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AN3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AN3" s="5" t="s">
+      <c r="AO3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AS3" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AT3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AU3" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:48" ht="36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" ht="40" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -1127,68 +1138,69 @@
       <c r="D4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="10"/>
+      <c r="K4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="10">
+      <c r="L4" s="10">
         <v>43250</v>
       </c>
-      <c r="L4" s="6">
+      <c r="M4" s="6">
         <v>1</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>1</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="3">
         <v>2018</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AM4" s="3">
         <v>2018</v>
       </c>
-      <c r="AU4" s="3" t="s">
+      <c r="AV4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AV4" s="3" t="s">
+      <c r="AW4" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:48" ht="36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" ht="40" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>60</v>
       </c>
@@ -1198,69 +1210,70 @@
       <c r="G5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="10"/>
+      <c r="K5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K5" s="10">
+      <c r="L5" s="10">
         <v>43250</v>
       </c>
-      <c r="L5" s="6">
+      <c r="M5" s="6">
         <v>2</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>1</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>2018</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="S5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="X5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AE5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AF5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AG5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AH5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AM5" s="3">
         <v>2018</v>
       </c>
-      <c r="AQ5" s="3" t="s">
+      <c r="AR5" s="3" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Y2" r:id="rId1" xr:uid="{DBCC3B5E-B159-476E-AF61-D5A86DF035F7}"/>
-    <hyperlink ref="Z2" r:id="rId2" xr:uid="{638B2B89-926A-45FF-91C3-A7F53C752A27}"/>
-    <hyperlink ref="Z3" r:id="rId3" xr:uid="{7951F308-EFBA-474A-9850-9C54BD14E4F9}"/>
+    <hyperlink ref="Z2" r:id="rId1" xr:uid="{DBCC3B5E-B159-476E-AF61-D5A86DF035F7}"/>
+    <hyperlink ref="AA2" r:id="rId2" xr:uid="{638B2B89-926A-45FF-91C3-A7F53C752A27}"/>
+    <hyperlink ref="AA3" r:id="rId3" xr:uid="{7951F308-EFBA-474A-9850-9C54BD14E4F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
